--- a/ai_checker/output/result.xlsx
+++ b/ai_checker/output/result.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>log值</t>
+          <t>log값</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/ai_checker/output/result.xlsx
+++ b/ai_checker/output/result.xlsx
@@ -461,10 +461,14 @@
           <t>SYNCO Wireless Microphone</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SYNCO Wireless Microphone</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -479,10 +483,14 @@
           <t>G4 Pro</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G4 Pro</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -493,7 +501,11 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>麦克风</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>否</t>
@@ -511,10 +523,14 @@
           <t>SYNCO</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SYNCO</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -529,10 +545,14 @@
           <t>Zhiying Technology</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Zhiying Technology</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -547,10 +567,14 @@
           <t>1.0.0</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.0.0</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -561,7 +585,11 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025/06/17</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>否</t>
@@ -579,10 +607,14 @@
           <t>Microphone/Zhiying Technology/SYNCO/G Series/OpenHarmony-5.1.0.0/G4 Pro/1.0.0/12/version/debug:nolog</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Microphone/Zhiying Technology/SYNCO/G Series/OpenHarmony-5.1.0.0/G4 Pro/1.0.0/12/version/debug:nolog</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -597,10 +629,14 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -615,10 +651,14 @@
           <t>OpenHarmony-5.1.0.0</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OpenHarmony 5.1.0 Release</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>

--- a/ai_checker/output/result.xlsx
+++ b/ai_checker/output/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,106 +453,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MarketName</t>
+          <t>Manufacture</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SYNCO Wireless Microphone</t>
+          <t>HYPCON</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SYNCO Wireless Microphone</t>
+          <t>HYPCON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ProductModel</t>
+          <t>OsFullName</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>G4 Pro</t>
+          <t>OpenHarmony-5.1.0.108</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G4 Pro</t>
+          <t>OpenHarmony 5.1.0 Release</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DeviceType</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>MarketName</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FCS200系列控制器</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>麦克风</t>
+          <t>FCS200系列控制器</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brand</t>
+          <t>ProductModel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SYNCO</t>
+          <t>CS210</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SYNCO</t>
+          <t>CS210</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Manufacture</t>
+          <t>Brand</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zhiying Technology</t>
+          <t>HYPCON</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zhiying Technology</t>
+          <t>HYPCON</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -564,57 +568,61 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>V1.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0.0</t>
+          <t>V1.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SecurityPatchTag</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>VersionId</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>DDC/HYPCON/HYPCON/CS210/OpenHarmony-5.1.0.108/CS210/CS210/18/1.0.0.0/default</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025/06/17</t>
+          <t>DDC/HYPCON/HYPCON/CS210/OpenHarmony-5.1.0.108/CS210/CS210/18/1.0.0.0/default</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VersionId</t>
+          <t>SecurityPatchTag</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microphone/Zhiying Technology/SYNCO/G Series/OpenHarmony-5.1.0.0/G4 Pro/1.0.0/12/version/debug:nolog</t>
+          <t>2025/05/01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Microphone/Zhiying Technology/SYNCO/G Series/OpenHarmony-5.1.0.0/G4 Pro/1.0.0/12/version/debug:nolog</t>
+          <t>2025/05/01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
@@ -636,29 +644,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OsFullName</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OpenHarmony-5.1.0.0</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>OpenHarmony 5.1.0 Release</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
     </row>
